--- a/Data/Libro1.xlsx
+++ b/Data/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RepoBryan\PlaywrightWeb\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDC7C11-018E-4975-8715-A7C2677ADF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5BC73F-D4AC-4CB6-8B9A-669A904B20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11385" xr2:uid="{0F0F2079-ED20-4B40-AC2D-094F46A47EB9}"/>
   </bookViews>
@@ -36,25 +36,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Correo</t>
   </si>
   <si>
-    <t>bryan.nico.rowuihoiwjnv</t>
-  </si>
-  <si>
     <t>Clave</t>
   </si>
   <si>
     <t>clave234</t>
+  </si>
+  <si>
+    <t>clave235</t>
+  </si>
+  <si>
+    <t>bryan.nico.rojas</t>
+  </si>
+  <si>
+    <t>bryan.nico.rojasssss</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,6 +72,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -430,28 +442,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0207A3-62B3-46D8-93F2-CD006976259C}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="bryan.nico.rojas@gmail.com" xr:uid="{587A1BEA-C326-43F3-9F24-8139C40FCF69}"/>
+    <hyperlink ref="A3" r:id="rId2" display="bryan.nico.rojas@gmail.com" xr:uid="{775DDE76-6105-4A60-B259-6E7124D41403}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Libro1.xlsx
+++ b/Data/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RepoBryan\PlaywrightWeb\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5BC73F-D4AC-4CB6-8B9A-669A904B20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC98D75-2E36-457F-BC36-2A92621BA9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11385" xr2:uid="{0F0F2079-ED20-4B40-AC2D-094F46A47EB9}"/>
   </bookViews>
@@ -47,13 +47,13 @@
     <t>clave234</t>
   </si>
   <si>
-    <t>clave235</t>
+    <t>bryan@gmail.com</t>
   </si>
   <si>
-    <t>bryan.nico.rojas</t>
+    <t>bryan.nico.rojas@gmail.com</t>
   </si>
   <si>
-    <t>bryan.nico.rojasssss</t>
+    <t>1075252464Rebel8!!</t>
   </si>
 </sst>
 </file>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0207A3-62B3-46D8-93F2-CD006976259C}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.28515625" customWidth="1"/>
@@ -458,7 +458,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -466,17 +466,35 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="bryan.nico.rojas@gmail.com" xr:uid="{587A1BEA-C326-43F3-9F24-8139C40FCF69}"/>
-    <hyperlink ref="A3" r:id="rId2" display="bryan.nico.rojas@gmail.com" xr:uid="{775DDE76-6105-4A60-B259-6E7124D41403}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{587A1BEA-C326-43F3-9F24-8139C40FCF69}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{775DDE76-6105-4A60-B259-6E7124D41403}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
